--- a/artfynd/A 7757-2021 artfynd.xlsx
+++ b/artfynd/A 7757-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7757-2021 artfynd.xlsx
+++ b/artfynd/A 7757-2021 artfynd.xlsx
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
@@ -1902,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
@@ -2026,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
